--- a/model_performance.xlsx
+++ b/model_performance.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -1035,14 +1035,14 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>, Too few data points 2,             threshold=10</t>
+          <t>, Too few data points 3,             threshold=10</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2192,14 +2192,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.601</v>
+        <v>0.662</v>
       </c>
       <c r="H15" t="n">
-        <v>132.345</v>
+        <v>129.005</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2213,17 +2213,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>227.09521961818027</t>
+          <t>223.3760691490834</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>258.2307692307692</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2242,23 +2242,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101, 180, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.633</v>
+        <v>0.063</v>
       </c>
       <c r="H16" t="n">
-        <v>132.481</v>
+        <v>271.702</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>alpha: 1.592</t>
+          <t>alpha: 25.950</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,11 +2268,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>235.19944106162572</t>
+          <t>98.62567168321515</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>347.8666666666666</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3593,18 +3593,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.661</v>
+        <v>0.717</v>
       </c>
       <c r="H15" t="n">
-        <v>122.129</v>
+        <v>115.605</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>alpha: 0.756</t>
+          <t>alpha: 0.521</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3614,17 +3614,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>217.37159524251715</t>
+          <t>217.91958771301793</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>258.2307692307692</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3643,23 +3643,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101, 180, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.68</v>
+        <v>0.111</v>
       </c>
       <c r="H16" t="n">
-        <v>121.734</v>
+        <v>264.941</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>alpha: 2.310</t>
+          <t>alpha: 21.544</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3669,11 +3669,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>227.0354103799608</t>
+          <t>110.2152473964851</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>347.8666666666667</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -4310,7 +4310,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -4334,18 +4334,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-0.458</v>
+        <v>0.28</v>
       </c>
       <c r="H3" t="n">
-        <v>275.813</v>
+        <v>204.203</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>alpha: 45.349</t>
+          <t>alpha: 0.000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31.765931527174462</t>
+          <t>119.24475792129078</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>266.8333333333333</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -4384,23 +4384,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101, 180, 801, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.457</v>
+        <v>-0.083</v>
       </c>
       <c r="H4" t="n">
-        <v>219.728</v>
+        <v>271.08</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>alpha: 0.000</t>
+          <t>alpha: 890.215</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -4410,11 +4410,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>171.33264707924624</t>
+          <t>4.329525048026561</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>361.6428571428572</v>
+        <v>366.3125</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
@@ -4585,7 +4585,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -4609,14 +4609,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-0.468</v>
+        <v>0.258</v>
       </c>
       <c r="H8" t="n">
-        <v>249.815</v>
+        <v>220.592</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4630,11 +4630,11 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.3786161055528987</t>
+          <t>47.168642597861435</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>266.8333333333333</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -4714,19 +4714,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>45, 47, 70, 101, 180, 198, 360, 376, 801, 817, 839, 844</t>
+          <t>45, 47, 70, 101, 180, 198, 360, 801, 817, 839, 844</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47, 101, 182, 360, 801, 839</t>
+          <t>101, 180, 182, 376</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.257</v>
+        <v>-1.466</v>
       </c>
       <c r="H10" t="n">
-        <v>245.749</v>
+        <v>139.363</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -4740,11 +4740,11 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>86.44180551156856</t>
+          <t>123.1391079866033</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>368.3</v>
+        <v>389.4782608695652</v>
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-0.97</v>
+        <v>-0.02</v>
       </c>
       <c r="H15" t="n">
-        <v>442.207</v>
+        <v>245.109</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -5015,17 +5015,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.10334349660199113</t>
+          <t>0.14084838029325208</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>250.4545454545455</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -5044,23 +5044,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>180, 360, 801, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.006</v>
+        <v>-0.036</v>
       </c>
       <c r="H16" t="n">
-        <v>191.083</v>
+        <v>239.257</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>alpha: 8.498</t>
+          <t>alpha: 0.521</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>88.29844163138056</t>
+          <t>161.9194313215687</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>329.6666666666667</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -5300,7 +5300,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -5324,14 +5324,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-0.481</v>
+        <v>-0.02</v>
       </c>
       <c r="H21" t="n">
-        <v>250.722</v>
+        <v>245.071</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -5349,13 +5349,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>266.8333333333333</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -5374,19 +5374,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>101, 180, 801, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.216</v>
+        <v>-0.002</v>
       </c>
       <c r="H22" t="n">
-        <v>260.848</v>
+        <v>229.469</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -5400,11 +5400,11 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>137.54740518573553</t>
+          <t>171.7532024003461</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>361.6428571428572</v>
+        <v>366.3125</v>
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -6395,14 +6395,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-0.152</v>
+        <v>-0.02</v>
       </c>
       <c r="H15" t="n">
-        <v>229.488</v>
+        <v>245.06</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -6416,17 +6416,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.17211937168130678</t>
+          <t>0.18998314474811892</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>258.2307692307692</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -6445,23 +6445,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101, 180, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.003</v>
+        <v>-0.019</v>
       </c>
       <c r="H16" t="n">
-        <v>263.85</v>
+        <v>233</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>alpha: 12.328</t>
+          <t>alpha: 0.000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -6471,11 +6471,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>106.36243865880506</t>
+          <t>179.33774809063294</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>347.8666666666667</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -7772,7 +7772,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -7796,14 +7796,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.702</v>
+        <v>0.833</v>
       </c>
       <c r="H15" t="n">
-        <v>119.93</v>
+        <v>99.61199999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -7817,17 +7817,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>218.9602845792983</t>
+          <t>209.58933556092558</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>258.2307692307692</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -7846,19 +7846,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101, 180, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.491</v>
+        <v>0.381</v>
       </c>
       <c r="H16" t="n">
-        <v>178.03</v>
+        <v>201.186</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -7872,11 +7872,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>222.1795726154599</t>
+          <t>207.88659056180353</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>347.8666666666667</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -9197,14 +9197,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.785</v>
+        <v>0.892</v>
       </c>
       <c r="H15" t="n">
-        <v>115.092</v>
+        <v>96.43600000000001</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -9218,17 +9218,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>225.29429030656817</t>
+          <t>215.71115862329873</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>258.2307692307692</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -9247,19 +9247,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101, 180, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.702</v>
+        <v>0.571</v>
       </c>
       <c r="H16" t="n">
-        <v>140.655</v>
+        <v>175.359</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9273,11 +9273,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>253.54130758101763</t>
+          <t>235.4469012857934</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>347.8666666666667</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -10574,7 +10574,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10598,14 +10598,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.822</v>
+        <v>0.897</v>
       </c>
       <c r="H15" t="n">
-        <v>106.094</v>
+        <v>85.44</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -10619,17 +10619,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>242.32107799996493</t>
+          <t>234.31245840147426</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>258.2307692307692</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10648,19 +10648,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101, 180, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.821</v>
+        <v>0.618</v>
       </c>
       <c r="H16" t="n">
-        <v>111.796</v>
+        <v>171.956</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -10674,11 +10674,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>275.39596074240444</t>
+          <t>255.5103906165956</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>347.8666666666667</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -11975,7 +11975,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -11999,14 +11999,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.619</v>
+        <v>0.702</v>
       </c>
       <c r="H15" t="n">
-        <v>147.845</v>
+        <v>129.164</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -12020,17 +12020,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>226.23938907260063</t>
+          <t>220.59347502585626</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>258.2307692307692</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -12049,23 +12049,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101, 180, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.709</v>
+        <v>0.126</v>
       </c>
       <c r="H16" t="n">
-        <v>123.266</v>
+        <v>261.322</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>alpha: 0.000</t>
+          <t>alpha: 10.235</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -12075,11 +12075,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>268.17594217104875</t>
+          <t>160.3236572361188</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>347.8666666666667</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -13376,7 +13376,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -13400,14 +13400,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.498</v>
+        <v>0.581</v>
       </c>
       <c r="H15" t="n">
-        <v>157.907</v>
+        <v>146.367</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -13421,17 +13421,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>221.04878632133548</t>
+          <t>216.92172831394137</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>258.2307692307692</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -13450,23 +13450,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101, 180, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.5669999999999999</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>147.203</v>
+        <v>279.186</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>alpha: 0.206</t>
+          <t>alpha: 31.257</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -13476,11 +13476,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>252.53941212722285</t>
+          <t>87.7299223848351</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>347.8666666666667</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -14777,7 +14777,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -14801,14 +14801,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>101, 180, 360, 839</t>
+          <t>101, 180, 839</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.515</v>
+        <v>0.587</v>
       </c>
       <c r="H15" t="n">
-        <v>143.259</v>
+        <v>142.946</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -14822,17 +14822,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>223.73825397054267</t>
+          <t>220.17002383553245</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>258.2307692307692</v>
+        <v>261.6428571428572</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -14851,23 +14851,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47, 101, 180, 360, 801, 839</t>
+          <t>47, 101, 360, 801, 839</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101, 180, 839</t>
+          <t>47, 180, 839</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="H16" t="n">
-        <v>150.907</v>
+        <v>277.7</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>alpha: 1.592</t>
+          <t>alpha: 31.257</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -14877,11 +14877,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>234.09915111798733</t>
+          <t>87.95301488808533</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>347.8666666666667</v>
+        <v>366.3125</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
